--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1006,653 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122018641</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79710</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bengtsdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>564758</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6992487</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122018337</v>
+      </c>
+      <c r="B6" t="n">
+        <v>55967</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bengtdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565102</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6992060</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122018026</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bengtdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564801</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6992447</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122018182</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90760</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bengtdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564788</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6992501</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122018053</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bengtdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564837</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6992346</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122018035</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bengtdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564808</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6992375</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121995314</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>90760</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121995302</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>90760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>121995292</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>90760</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122018641</v>
+        <v>122018337</v>
       </c>
       <c r="B5" t="n">
-        <v>79710</v>
+        <v>55967</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,34 +1024,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bengtsdalsbäcken, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564758</v>
+        <v>565102</v>
       </c>
       <c r="R5" t="n">
-        <v>6992487</v>
+        <v>6992060</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1110,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122018337</v>
+        <v>122018182</v>
       </c>
       <c r="B6" t="n">
-        <v>55967</v>
+        <v>90760</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,27 +1130,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565102</v>
+        <v>564788</v>
       </c>
       <c r="R6" t="n">
-        <v>6992060</v>
+        <v>6992501</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1198,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122018182</v>
+        <v>122018053</v>
       </c>
       <c r="B8" t="n">
-        <v>90760</v>
+        <v>57365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,26 +1347,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564788</v>
+        <v>564837</v>
       </c>
       <c r="R8" t="n">
-        <v>6992501</v>
+        <v>6992346</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1408,13 +1413,17 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1433,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122018053</v>
+        <v>122018035</v>
       </c>
       <c r="B9" t="n">
         <v>57365</v>
@@ -1477,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564837</v>
+        <v>564808</v>
       </c>
       <c r="R9" t="n">
-        <v>6992346</v>
+        <v>6992375</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1544,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122018035</v>
+        <v>122018641</v>
       </c>
       <c r="B10" t="n">
-        <v>57365</v>
+        <v>79710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,38 +1569,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Bengtsdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564808</v>
+        <v>564758</v>
       </c>
       <c r="R10" t="n">
-        <v>6992375</v>
+        <v>6992487</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1624,11 +1629,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122018337</v>
+        <v>122018053</v>
       </c>
       <c r="B5" t="n">
-        <v>55974</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565102</v>
+        <v>564837</v>
       </c>
       <c r="R5" t="n">
-        <v>6992060</v>
+        <v>6992346</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1088,6 +1088,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122018026</v>
+        <v>122018182</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>90797</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,27 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564801</v>
+        <v>564788</v>
       </c>
       <c r="R6" t="n">
-        <v>6992447</v>
+        <v>6992501</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1196,17 +1200,13 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122018035</v>
+        <v>122018337</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>55974</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564808</v>
+        <v>565102</v>
       </c>
       <c r="R7" t="n">
-        <v>6992375</v>
+        <v>6992060</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1305,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122018053</v>
+        <v>122018026</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1380,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564837</v>
+        <v>564801</v>
       </c>
       <c r="R8" t="n">
-        <v>6992346</v>
+        <v>6992447</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1447,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122018182</v>
+        <v>122018035</v>
       </c>
       <c r="B9" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,26 +1458,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564788</v>
+        <v>564808</v>
       </c>
       <c r="R9" t="n">
-        <v>6992501</v>
+        <v>6992375</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1528,13 +1524,17 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121995314</v>
+        <v>121995302</v>
       </c>
       <c r="B2" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564957</v>
+        <v>564994</v>
       </c>
       <c r="R2" t="n">
-        <v>6992233</v>
+        <v>6992190</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -789,7 +789,7 @@
         <v>121995292</v>
       </c>
       <c r="B3" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121995302</v>
+        <v>121995314</v>
       </c>
       <c r="B4" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564994</v>
+        <v>564957</v>
       </c>
       <c r="R4" t="n">
-        <v>6992190</v>
+        <v>6992233</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122018053</v>
+        <v>122018337</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>55974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564837</v>
+        <v>565102</v>
       </c>
       <c r="R5" t="n">
-        <v>6992346</v>
+        <v>6992060</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1088,11 +1088,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122018182</v>
+        <v>122018035</v>
       </c>
       <c r="B6" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1130,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564788</v>
+        <v>564808</v>
       </c>
       <c r="R6" t="n">
-        <v>6992501</v>
+        <v>6992375</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1200,13 +1196,17 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122018337</v>
+        <v>122018053</v>
       </c>
       <c r="B7" t="n">
-        <v>55974</v>
+        <v>57374</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565102</v>
+        <v>564837</v>
       </c>
       <c r="R7" t="n">
-        <v>6992060</v>
+        <v>6992346</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1305,6 +1305,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122018026</v>
+        <v>122018182</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,27 +1352,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564801</v>
+        <v>564788</v>
       </c>
       <c r="R8" t="n">
-        <v>6992447</v>
+        <v>6992501</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1413,17 +1417,13 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122018035</v>
+        <v>122018026</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564808</v>
+        <v>564801</v>
       </c>
       <c r="R9" t="n">
-        <v>6992375</v>
+        <v>6992447</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1556,7 +1556,7 @@
         <v>122018641</v>
       </c>
       <c r="B10" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121995302</v>
+        <v>121995314</v>
       </c>
       <c r="B2" t="n">
         <v>90807</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564994</v>
+        <v>564957</v>
       </c>
       <c r="R2" t="n">
-        <v>6992190</v>
+        <v>6992233</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121995314</v>
+        <v>121995302</v>
       </c>
       <c r="B4" t="n">
         <v>90807</v>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564957</v>
+        <v>564994</v>
       </c>
       <c r="R4" t="n">
-        <v>6992233</v>
+        <v>6992190</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122018337</v>
+        <v>122018053</v>
       </c>
       <c r="B5" t="n">
-        <v>55974</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565102</v>
+        <v>564837</v>
       </c>
       <c r="R5" t="n">
-        <v>6992060</v>
+        <v>6992346</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1088,6 +1088,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122018035</v>
+        <v>122018337</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>55974</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564808</v>
+        <v>565102</v>
       </c>
       <c r="R6" t="n">
-        <v>6992375</v>
+        <v>6992060</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1194,11 +1199,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122018053</v>
+        <v>122018182</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1241,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564837</v>
+        <v>564788</v>
       </c>
       <c r="R7" t="n">
-        <v>6992346</v>
+        <v>6992501</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1307,17 +1306,13 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1336,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122018182</v>
+        <v>122018641</v>
       </c>
       <c r="B8" t="n">
-        <v>90807</v>
+        <v>79727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,37 +1347,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Bengtsdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564788</v>
+        <v>564758</v>
       </c>
       <c r="R8" t="n">
-        <v>6992501</v>
+        <v>6992487</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1423,7 +1415,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1553,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122018641</v>
+        <v>122018035</v>
       </c>
       <c r="B10" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,34 +1560,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bengtsdalsbäcken, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564758</v>
+        <v>564808</v>
       </c>
       <c r="R10" t="n">
-        <v>6992487</v>
+        <v>6992375</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,6 +1624,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121995314</v>
+        <v>121995292</v>
       </c>
       <c r="B2" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564957</v>
+        <v>564959</v>
       </c>
       <c r="R2" t="n">
-        <v>6992233</v>
+        <v>6992220</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121995292</v>
+        <v>121995302</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564959</v>
+        <v>564994</v>
       </c>
       <c r="R3" t="n">
-        <v>6992220</v>
+        <v>6992190</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121995302</v>
+        <v>121995314</v>
       </c>
       <c r="B4" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564994</v>
+        <v>564957</v>
       </c>
       <c r="R4" t="n">
-        <v>6992190</v>
+        <v>6992233</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122018053</v>
+        <v>122018026</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564837</v>
+        <v>564801</v>
       </c>
       <c r="R5" t="n">
-        <v>6992346</v>
+        <v>6992447</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122018337</v>
+        <v>122018182</v>
       </c>
       <c r="B6" t="n">
-        <v>55974</v>
+        <v>90819</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,27 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565102</v>
+        <v>564788</v>
       </c>
       <c r="R6" t="n">
-        <v>6992060</v>
+        <v>6992501</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1207,6 +1206,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122018182</v>
+        <v>122018641</v>
       </c>
       <c r="B7" t="n">
-        <v>90807</v>
+        <v>79732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,37 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Bengtsdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564788</v>
+        <v>564758</v>
       </c>
       <c r="R7" t="n">
-        <v>6992501</v>
+        <v>6992487</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1312,7 +1309,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1331,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122018641</v>
+        <v>122018035</v>
       </c>
       <c r="B8" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,34 +1343,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bengtsdalsbäcken, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564758</v>
+        <v>564808</v>
       </c>
       <c r="R8" t="n">
-        <v>6992487</v>
+        <v>6992375</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1407,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122018026</v>
+        <v>122018053</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564801</v>
+        <v>564837</v>
       </c>
       <c r="R9" t="n">
-        <v>6992447</v>
+        <v>6992346</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1544,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122018035</v>
+        <v>122018337</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>55979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,21 +1565,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564808</v>
+        <v>565102</v>
       </c>
       <c r="R10" t="n">
-        <v>6992375</v>
+        <v>6992060</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1624,11 +1629,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121995292</v>
+        <v>121995302</v>
       </c>
       <c r="B2" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564959</v>
+        <v>564994</v>
       </c>
       <c r="R2" t="n">
-        <v>6992220</v>
+        <v>6992190</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121995302</v>
+        <v>121995292</v>
       </c>
       <c r="B3" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564994</v>
+        <v>564959</v>
       </c>
       <c r="R3" t="n">
-        <v>6992190</v>
+        <v>6992220</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -900,7 +900,7 @@
         <v>121995314</v>
       </c>
       <c r="B4" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>122018182</v>
       </c>
       <c r="B6" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122018035</v>
+        <v>122018053</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564808</v>
+        <v>564837</v>
       </c>
       <c r="R8" t="n">
-        <v>6992375</v>
+        <v>6992346</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122018053</v>
+        <v>122018337</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>55979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564837</v>
+        <v>565102</v>
       </c>
       <c r="R9" t="n">
-        <v>6992346</v>
+        <v>6992060</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1518,11 +1518,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122018337</v>
+        <v>122018035</v>
       </c>
       <c r="B10" t="n">
-        <v>55979</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,21 +1560,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565102</v>
+        <v>564808</v>
       </c>
       <c r="R10" t="n">
-        <v>6992060</v>
+        <v>6992375</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,6 +1624,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,6 +1653,121 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124049961</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bengtdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564656</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6992669</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,6 +1768,685 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128161076</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564685</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6992596</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128160946</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564620</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6992823</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128161057</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564695</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6992662</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128160915</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>564558</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6992870</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128161120</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>564958</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6992226</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128161000</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>564748</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6992577</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128161032</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>564684</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6992649</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>128160946</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128161057</v>
       </c>
       <c r="B14" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128160915</v>
       </c>
       <c r="B15" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128161120</v>
       </c>
       <c r="B16" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>128161000</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128161032</v>
       </c>
       <c r="B18" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>128160946</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128161057</v>
       </c>
       <c r="B14" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128160915</v>
       </c>
       <c r="B15" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128161120</v>
       </c>
       <c r="B16" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>128161000</v>
       </c>
       <c r="B17" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128161032</v>
       </c>
       <c r="B18" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1773,7 +1773,7 @@
         <v>128161076</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128160946</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128161057</v>
       </c>
       <c r="B14" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128160915</v>
+        <v>128161120</v>
       </c>
       <c r="B15" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,14 +2092,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564558</v>
+        <v>564958</v>
       </c>
       <c r="R15" t="n">
-        <v>6992870</v>
+        <v>6992226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128161120</v>
+        <v>128160915</v>
       </c>
       <c r="B16" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,14 +2189,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564958</v>
+        <v>564558</v>
       </c>
       <c r="R16" t="n">
-        <v>6992226</v>
+        <v>6992870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
         <v>128161000</v>
       </c>
       <c r="B17" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128161032</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1773,7 +1773,7 @@
         <v>128161076</v>
       </c>
       <c r="B12" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128160946</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128161057</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128161120</v>
+        <v>128160915</v>
       </c>
       <c r="B15" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,14 +2092,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564958</v>
+        <v>564558</v>
       </c>
       <c r="R15" t="n">
-        <v>6992226</v>
+        <v>6992870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128160915</v>
+        <v>128161120</v>
       </c>
       <c r="B16" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,14 +2189,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564558</v>
+        <v>564958</v>
       </c>
       <c r="R16" t="n">
-        <v>6992870</v>
+        <v>6992226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
         <v>128161000</v>
       </c>
       <c r="B17" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128161032</v>
       </c>
       <c r="B18" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1773,7 +1773,7 @@
         <v>128161076</v>
       </c>
       <c r="B12" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128160946</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128161057</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128160915</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128161120</v>
       </c>
       <c r="B16" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>128161000</v>
       </c>
       <c r="B17" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128161032</v>
       </c>
       <c r="B18" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1773,7 +1773,7 @@
         <v>128161076</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128160946</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128161057</v>
       </c>
       <c r="B14" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128160915</v>
       </c>
       <c r="B15" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128161120</v>
       </c>
       <c r="B16" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>128161000</v>
       </c>
       <c r="B17" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128161032</v>
       </c>
       <c r="B18" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>128160946</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128160915</v>
+        <v>128161120</v>
       </c>
       <c r="B15" t="n">
         <v>91484</v>
@@ -2092,14 +2092,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564558</v>
+        <v>564958</v>
       </c>
       <c r="R15" t="n">
-        <v>6992870</v>
+        <v>6992226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128161120</v>
+        <v>128160915</v>
       </c>
       <c r="B16" t="n">
         <v>91484</v>
@@ -2189,14 +2189,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564958</v>
+        <v>564558</v>
       </c>
       <c r="R16" t="n">
-        <v>6992226</v>
+        <v>6992870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 5269-2024 artfynd.xlsx
+++ b/artfynd/A 5269-2024 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>128160946</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>128161057</v>
       </c>
       <c r="B14" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128161120</v>
+        <v>128160915</v>
       </c>
       <c r="B15" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,14 +2092,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
+          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564958</v>
+        <v>564558</v>
       </c>
       <c r="R15" t="n">
-        <v>6992226</v>
+        <v>6992870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128160915</v>
+        <v>128161120</v>
       </c>
       <c r="B16" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,14 +2189,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jonas-Gustavsänget, Jonas-Gustavsänget, Jmt</t>
+          <t>Bengtsdalsbäcken, Bengtsdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564558</v>
+        <v>564958</v>
       </c>
       <c r="R16" t="n">
-        <v>6992870</v>
+        <v>6992226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
         <v>128161000</v>
       </c>
       <c r="B17" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128161032</v>
       </c>
       <c r="B18" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
